--- a/artfynd/A 10744-2024 artfynd.xlsx
+++ b/artfynd/A 10744-2024 artfynd.xlsx
@@ -1844,7 +1844,7 @@
         <v>117832013</v>
       </c>
       <c r="B13" t="n">
-        <v>102761</v>
+        <v>102763</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 10744-2024 artfynd.xlsx
+++ b/artfynd/A 10744-2024 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
